--- a/data/trans_dic/P1417-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1417-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,22 +737,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,23</t>
+          <t>0,23; 2,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,98</t>
+          <t>0,5; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,5</t>
+          <t>0,8; 6,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,1</t>
+          <t>0,11; 1,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,9</t>
+          <t>0,47; 1,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,92</t>
+          <t>0,29; 2,82</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,76</t>
+          <t>0,66; 2,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,21</t>
+          <t>0,94; 3,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,34</t>
+          <t>1,03; 3,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,96</t>
+          <t>1,17; 4,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,3</t>
+          <t>0,37; 1,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,59</t>
+          <t>0,46; 1,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,69</t>
+          <t>0,51; 1,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,12</t>
+          <t>0,58; 1,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,33</t>
+          <t>0,33; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,12</t>
+          <t>0,87; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,62</t>
+          <t>2,72; 5,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,51</t>
+          <t>1,19; 3,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,45</t>
+          <t>4,43; 7,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,71</t>
+          <t>0,57; 1,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,03</t>
+          <t>1,46; 2,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,88</t>
+          <t>0,74; 1,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,39</t>
+          <t>2,47; 4,25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,55</t>
+          <t>0,16; 1,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,93</t>
+          <t>0,12; 1,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,46</t>
+          <t>0,56; 2,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,2</t>
+          <t>1,38; 4,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,82</t>
+          <t>1,16; 3,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,73</t>
+          <t>4,47; 7,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,48</t>
+          <t>0,45; 1,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,32</t>
+          <t>0,88; 2,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,11</t>
+          <t>0,81; 2,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,43</t>
+          <t>2,53; 4,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,63</t>
+          <t>0,91; 2,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,17</t>
+          <t>1,03; 4,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,21</t>
+          <t>1,38; 4,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,43</t>
+          <t>1,36; 4,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,84</t>
+          <t>1,83; 4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,08</t>
+          <t>0,53; 2,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,6</t>
+          <t>0,84; 2,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,6</t>
+          <t>0,87; 2,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,84</t>
+          <t>1,53; 2,88</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,87</t>
+          <t>0,54; 4,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,25</t>
+          <t>0,67; 4,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,05</t>
+          <t>0,56; 3,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,48</t>
+          <t>1,64; 4,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,81</t>
+          <t>0,81; 3,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,45</t>
+          <t>1,68; 5,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,95</t>
+          <t>1,61; 5,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,6</t>
+          <t>2,13; 4,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,06</t>
+          <t>0,83; 3,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,04</t>
+          <t>1,49; 4,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,7</t>
+          <t>1,42; 3,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,43</t>
+          <t>2,22; 3,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,79</t>
+          <t>0,5; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,83</t>
+          <t>0,62; 3,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,38</t>
+          <t>2,87; 6,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,86</t>
+          <t>2,03; 6,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,29</t>
+          <t>2,28; 6,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,18</t>
+          <t>2,55; 6,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 10,53</t>
+          <t>6,79; 10,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,16</t>
+          <t>1,83; 5,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,39</t>
+          <t>1,69; 4,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,08</t>
+          <t>2,07; 5,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,41</t>
+          <t>5,55; 8,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,67</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,68</t>
+          <t>0,24; 0,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,87</t>
+          <t>0,36; 0,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,45</t>
+          <t>0,97; 1,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,2</t>
+          <t>1,29; 2,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,34</t>
+          <t>2,22; 3,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,04</t>
+          <t>1,95; 3,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,94</t>
+          <t>3,93; 5,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,35</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,89</t>
+          <t>1,35; 1,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,88</t>
+          <t>1,26; 1,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,09</t>
+          <t>2,6; 3,29</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9531</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4675</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6065</t>
+          <t>0; 7202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4585</t>
+          <t>0; 4994</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>972; 9615</t>
+          <t>1011; 9495</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1973; 11813</t>
+          <t>1984; 12674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2195; 26631</t>
+          <t>2893; 23590</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6468</t>
+          <t>0; 6448</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1050; 9687</t>
+          <t>986; 9884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3308; 15487</t>
+          <t>3802; 15352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2195; 27928</t>
+          <t>2234; 21737</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11295</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5045</t>
+          <t>0; 5053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5373</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 5104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2296,42 +2296,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4763; 17290</t>
+          <t>4141; 17830</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5156; 19588</t>
+          <t>5722; 19737</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5309; 18802</t>
+          <t>5814; 18849</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5016; 20270</t>
+          <t>5863; 20346</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5254; 17640</t>
+          <t>5012; 18110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6040; 20608</t>
+          <t>5978; 21091</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6756; 19549</t>
+          <t>5890; 20563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5132; 19839</t>
+          <t>5717; 18824</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>41499</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6244</t>
+          <t>0; 6974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7936</t>
+          <t>0; 8624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2116; 12500</t>
+          <t>2028; 12390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6401; 21546</t>
+          <t>6004; 21962</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18677; 39908</t>
+          <t>19305; 40350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8166; 23199</t>
+          <t>7878; 22280</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22687; 40371</t>
+          <t>27522; 47557</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6986; 22668</t>
+          <t>7547; 23564</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20925; 42176</t>
+          <t>20326; 40532</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9228; 25066</t>
+          <t>9790; 25459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27348; 47326</t>
+          <t>30694; 52827</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>45808</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5534</t>
+          <t>0; 6433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>971; 9504</t>
+          <t>954; 8475</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1000; 9290</t>
+          <t>0; 9273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>451; 8215</t>
+          <t>826; 8664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2888; 12666</t>
+          <t>2907; 13592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9351; 25779</t>
+          <t>8479; 24868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7502; 24772</t>
+          <t>7528; 24273</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28033; 47939</t>
+          <t>32918; 52759</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3797; 15306</t>
+          <t>4661; 15804</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11459; 28471</t>
+          <t>10858; 29912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10415; 27289</t>
+          <t>10543; 28052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24235; 54870</t>
+          <t>36340; 59054</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>26031</t>
         </is>
       </c>
     </row>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7004</t>
+          <t>0; 7079</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7497</t>
+          <t>0; 7600</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4156; 14721</t>
+          <t>5526; 16967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4130; 16860</t>
+          <t>4175; 16342</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6160; 18870</t>
+          <t>6181; 19542</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6183; 21987</t>
+          <t>6752; 22204</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9850; 20871</t>
+          <t>11066; 24897</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4123; 16419</t>
+          <t>4197; 16782</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7218; 22764</t>
+          <t>7406; 23224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8132; 25328</t>
+          <t>8478; 25587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15816; 31334</t>
+          <t>18542; 34906</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>25049</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>945; 11320</t>
+          <t>1592; 11896</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2918; 13163</t>
+          <t>2087; 13408</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1035; 10196</t>
+          <t>1877; 10520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6156; 16459</t>
+          <t>6646; 17658</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2882; 13067</t>
+          <t>2781; 13669</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4947; 19307</t>
+          <t>5939; 19460</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5985; 18707</t>
+          <t>6094; 20111</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4118; 21810</t>
+          <t>9303; 19938</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5482; 19429</t>
+          <t>5299; 19152</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9928; 26790</t>
+          <t>9878; 27996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9332; 26342</t>
+          <t>10119; 25929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12165; 33389</t>
+          <t>18684; 33027</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>48573</t>
+          <t>53024</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1609; 12148</t>
+          <t>1045; 11908</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6853</t>
+          <t>0; 7342</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1592; 9838</t>
+          <t>1585; 9385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7934; 17978</t>
+          <t>8870; 19990</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6821; 22917</t>
+          <t>6763; 21761</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8740; 24473</t>
+          <t>8880; 26470</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10095; 28751</t>
+          <t>10221; 27325</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28858; 44741</t>
+          <t>31499; 49312</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10119; 28054</t>
+          <t>9968; 27981</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10106; 28029</t>
+          <t>10823; 29664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13582; 33401</t>
+          <t>13621; 33487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39823; 59418</t>
+          <t>42893; 65524</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7344; 22078</t>
+          <t>7324; 22343</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9030; 23462</t>
+          <t>8302; 24472</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12136; 29576</t>
+          <t>12062; 30491</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26685; 50183</t>
+          <t>34099; 57097</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43609; 74177</t>
+          <t>43731; 75000</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77799; 118642</t>
+          <t>78955; 117794</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70214; 107871</t>
+          <t>68985; 106283</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>124627; 180486</t>
+          <t>146499; 189643</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54087; 89947</t>
+          <t>54059; 89366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89615; 132235</t>
+          <t>94271; 137955</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87871; 130168</t>
+          <t>87288; 128433</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>165015; 219937</t>
+          <t>189004; 238462</t>
         </is>
       </c>
     </row>
